--- a/important_mails_2026-04-17.xlsx
+++ b/important_mails_2026-04-17.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>其他风险类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,126 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
+          <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+          <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[Action Required] – Update Inventory -FBA</t>
+          <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家：
+我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
+【如何完成合规?】
+您必须与第三方检测、检验和认证服务提供商合作，对收到通知的所有 ASIN 进行商品检测或验证现有的检测文件。请按照以下步骤操作：
+1.前往【绩效】-【账户状况】-【政策合规性】，点击【食品和商品安全问题】。
+2.在【后续步骤】列下，针对需操作的商品点击【提交】-【验证您的商品】。
+3.从清单中选择第三方检测提供商（如需比价，可先查看【从多个提供商获取报价的说明】后再返回选择），点击继续。
+4.确认详细联系信息，点击【确认并继续】。
+5.复制生成的检测申请表编号，提供给所选提供商完成检测
+如果验证现有文件，您必须将由 ISO 17025 认可的实验室出具的检测报告提交至检测、检验和认证服务提供商。
+如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新” &gt; “验证您的商品”
+⚠️请注意：
+① 同一ASIN可能只在部分欧洲站点被触发通知，若您计划在欧洲（英国及欧盟）继续销售，只需为每个ASIN任选一个站点完成合规，测试结果将同步至全欧站点。
+② 由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。再次提醒您，为避免下架，请在截止日期之前确保TRF状态更新为【正在验证】或【已通过】。
+③ 如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
+感谢您的支持，祝您合规大卖！
+如有疑问，请扫码加入亚马逊卖家合规群：
+https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
+Amazon Global Selling Seller Compliance Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Verify your primary operating address for tax purposes</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Services
+ Verify your primary operating address for tax purposes
+ Hello,
+To ensure the pertinent tax treatment is applied to your account, you must confirm your primary operating address . To help you, we’ve introduced a new field in Seller Central, called primary operating address.
+This allows us to determine your establishment for tax purposes. If your information isn’t listed correctly, your taxes will also be incorrect.
+ Your primary operating address or primary place of business is the physical location where you conduct your main day-to-day business activities. This can be either:
+- Where your central administration functions take place.
+- Where you have sufficient degree of permanence and an established presence in terms of human resources, technical resources, and infrastructure to run your business operations (e.g., where your employees are located).
+ Here's how to verify your primary operating address:
+- Go to your Identity Information page .
+- If the pre-filled information is correct, click I confirm that my primary operating address is correct .
+- If it's incorrect, click Edit information and provide a valid primary operating address by selecting a saved address </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] – Update Inventory -FBA</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -530,39 +635,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -582,39 +687,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -631,39 +736,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -675,39 +780,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -730,39 +835,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -786,39 +891,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -837,39 +942,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -885,39 +990,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -929,39 +1034,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -981,39 +1086,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1031,90 +1136,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0FCDRNTT8" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-Once you have corrected the problems listed above, please re-upload a valid document in "Manage Your Compliance" on "Provide documents" section.
-For any questions/appeals regarding this product/other products, please submit them ( for each ASIN separately ) in "Manage Your Compliance" on the relevant Appeal reason:
-1. Go to the Performance tab and select Account health.
-2. Under Manage your compliance in the bottom right corner, click Product compliance requests.
-3. Click Add or appeal compliance button for the product you’re taking action on.
-4. To upload the documentation, drag and drop fil</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1128,39 +1182,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1179,40 +1233,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1223,57 +1277,6 @@
  Here’s how you can reduce returns and help customers:
  • Manufacturer support – A customer has a question about your product? They can contact your experts directly. In 2025, approximately 64% of customers who contacted support through Manufacturer support did not return their product. * Available in the US, Canada, UK, Germany, France, Italy, Spain, Belgium, Sweden, Poland and the Netherlands.
  • Brand integration – call &amp; chat – A customer runs into a setup issue and wants instant help? Provide live calls or chat support. In 2025, approximately 58% of customers who contacted support through Brand integration – call &amp; chat did not return the product. * Available in the US, Canada, UK, Germany, France, Italy, Spain, Belgium, Swe</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
- Reglamento relativo a la seguridad general de los productos</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
- Hola, Weihai EU:
- Algunos de los listings de nuestras tiendas de la UE se han desactivado debido a que falta información de cumplimiento normativo obligatoria. Esta medida no afecta al estado de tu cuenta.
- Encontrarás ejemplos de listings desactivados al final de este correo electrónico y la lista completa en la página "Estado de la cuenta". Revisa los listings afectados y siguientes pasos para cumplir los requisitos del Reglamento relativo a la seguridad general de los productos que se indican a continuación.
- Presentar información sobre cumplimiento normativo
- Presentar información sobre cumplimiento normativo
- ¿Cómo puedo reactivar mis listings?
- Para reactivar tus listings, proporciona la información obligatoria del Reglamento relativo a la seguridad general de los productos. Para ello, sigue las instrucciones que se indican a continuación:
--
- Ve a la página "Estado de la cuenta" .
-- Selecciona "Añadir filtros" y marca "Listing retirado" en la columna "Filtrar según las medidas tomadas".
-- Haz clic en "Enviar" junto al listing desactivado y sigue las</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1391,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>其他风险类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>older</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1403,69 +1406,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
+          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
+          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-C2S2 PCP Pallet Limited Time Promotion
-Dear Selling Partner,
-Ready to unlock European growth? Join Customs Clearance and Shipping Service (C2S2) PCP Pallets and get an unbeatable launch package: up to €240 in transportation fee reimbursements per shipment during our Spring Promotion (April 10 - June 30, 2026), PLUS 1 year of free Indirect Representation (IR) worth €200, PLUS your first shipment worth €60 completely free.
-It's the perfect time to start shipping cross-border with confidence. Join for free to the PCP-AVASK Pallet solution today.
-[Enroll now with AVASK](https://go.amazonsellerservices.com/e/229492/jfe-form-SV-cA1EXJ0WHz20OFg/7z2qvf2/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-- Automatic tracking: No claims process - we track your shipments automatically
-- Check full [terms and conditions here](https://go.amazonsellerservices.com/e/229492/-C2S2-LTL-Q2-Promotion-TCs-pdf/7z2qvf5/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-Offer Details:
-Pallets per Shipment                               Your Savings
-1-5 pallets    </t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1491,39 +1446,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1544,39 +1499,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1602,39 +1557,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1654,40 +1609,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1703,39 +1658,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1755,39 +1710,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1813,39 +1768,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1861,39 +1816,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1914,39 +1869,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -1961,39 +1916,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2007,40 +1962,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2057,39 +2012,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2109,39 +2064,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2158,39 +2113,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2213,39 +2168,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2265,39 +2220,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2314,39 +2269,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2360,6 +2315,57 @@
  ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
 Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
 Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
+ DOC REVIEW</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0FCDRNTT8" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+Once you have corrected the problems listed above, please re-upload a valid document in "Manage Your Compliance" on "Provide documents" section.
+For any questions/appeals regarding this product/other products, please submit them ( for each ASIN separately ) in "Manage Your Compliance" on the relevant Appeal reason:
+1. Go to the Performance tab and select Account health.
+2. Under Manage your compliance in the bottom right corner, click Product compliance requests.
+3. Click Add or appeal compliance button for the product you’re taking action on.
+4. To upload the documentation, drag and drop fil</t>
         </is>
       </c>
     </row>
@@ -3526,21 +3532,72 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
+          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
+          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
+ Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
+ Hola, Weihai EU:
+ Algunos de los listings de nuestras tiendas de la UE se han desactivado debido a que falta información de cumplimiento normativo obligatoria. Esta medida no afecta al estado de tu cuenta.
+ Encontrarás ejemplos de listings desactivados al final de este correo electrónico y la lista completa en la página "Estado de la cuenta". Revisa los listings afectados y siguientes pasos para cumplir los requisitos del Reglamento relativo a la seguridad general de los productos que se indican a continuación.
+ Presentar información sobre cumplimiento normativo
+ Presentar información sobre cumplimiento normativo
+ ¿Cómo puedo reactivar mis listings?
+ Para reactivar tus listings, proporciona la información obligatoria del Reglamento relativo a la seguridad general de los productos. Para ello, sigue las instrucciones que se indican a continuación:
+-
+ Ve a la página "Estado de la cuenta" .
+- Selecciona "Añadir filtros" y marca "Listing retirado" en la columna "Filtrar según las medidas tomadas".
+- Haz clic en "Enviar" junto al listing desactivado y sigue las</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -3573,39 +3630,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -3620,39 +3677,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -3671,39 +3728,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -3722,39 +3779,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -3766,39 +3823,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -3814,39 +3871,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -3858,39 +3915,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3905,39 +3962,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3949,39 +4006,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -3993,39 +4050,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4037,39 +4094,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4081,39 +4138,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4125,39 +4182,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4169,39 +4226,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4213,39 +4270,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4257,39 +4314,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4301,39 +4358,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4352,39 +4409,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4396,39 +4453,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4440,39 +4497,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4484,39 +4541,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4528,39 +4585,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4572,39 +4629,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4616,39 +4673,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4660,39 +4717,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4711,39 +4768,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4755,40 +4812,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4807,39 +4864,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4851,39 +4908,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4902,39 +4959,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -4966,39 +5023,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -5025,39 +5082,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -5069,39 +5126,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -5111,39 +5168,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -5153,39 +5210,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5215,39 +5272,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5265,39 +5322,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5314,39 +5371,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5362,39 +5419,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5423,39 +5480,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5476,39 +5533,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5523,39 +5580,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5569,40 +5626,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5618,39 +5675,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5666,39 +5723,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5714,39 +5771,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5762,40 +5819,40 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5811,39 +5868,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5861,39 +5918,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5909,39 +5966,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5956,39 +6013,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6003,39 +6060,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6056,40 +6113,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -6104,39 +6161,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -6157,39 +6214,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -6222,39 +6279,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6270,39 +6327,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6318,39 +6375,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6368,39 +6425,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6417,39 +6474,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6462,39 +6519,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6515,39 +6572,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6570,39 +6627,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6623,39 +6680,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6679,39 +6736,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6734,39 +6791,87 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
+C2S2 PCP Pallet Limited Time Promotion
+Dear Selling Partner,
+Ready to unlock European growth? Join Customs Clearance and Shipping Service (C2S2) PCP Pallets and get an unbeatable launch package: up to €240 in transportation fee reimbursements per shipment during our Spring Promotion (April 10 - June 30, 2026), PLUS 1 year of free Indirect Representation (IR) worth €200, PLUS your first shipment worth €60 completely free.
+It's the perfect time to start shipping cross-border with confidence. Join for free to the PCP-AVASK Pallet solution today.
+[Enroll now with AVASK](https://go.amazonsellerservices.com/e/229492/jfe-form-SV-cA1EXJ0WHz20OFg/7z2qvf2/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
+- Automatic tracking: No claims process - we track your shipments automatically
+- Check full [terms and conditions here](https://go.amazonsellerservices.com/e/229492/-C2S2-LTL-Q2-Promotion-TCs-pdf/7z2qvf5/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
+Offer Details:
+Pallets per Shipment                               Your Savings
+1-5 pallets    </t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -6786,39 +6891,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -6837,39 +6942,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -6878,39 +6983,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6928,39 +7033,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6990,39 +7095,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7038,39 +7143,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
